--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2019_tarapaca.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:05</t>
+    <t xml:space="preserve">2026-09-24 00:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -949,13 +949,13 @@
         <v>7</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="20">
@@ -972,13 +972,13 @@
         <v>7</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="21">
@@ -998,7 +998,7 @@
         <v>0.15</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.33</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2019_tarapaca.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:55</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2019_tarapaca.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-05 19:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
